--- a/templates/approved/3. ОЖР.xlsx
+++ b/templates/approved/3. ОЖР.xlsx
@@ -2697,10 +2697,10 @@
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="43" t="str">
-        <f>CONCATENATE(C2,",",C3)</f>
+        <f>IF(AND(C2="",C3=""),"",CONCATENATE(IF(C2="","",C2),",",IF(C3="","",C3)))</f>
       </c>
       <c r="D24" s="43" t="str">
-        <f>CONCATENATE(D2,",",D3)</f>
+        <f>IF(AND(D2="",D3=""),"",CONCATENATE(IF(D2="","",D2),",",IF(D3="","",D3)))</f>
       </c>
       <c r="E24" s="44"/>
     </row>
@@ -2710,100 +2710,100 @@
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="43" t="str">
-        <f>CONCATENATE(C1,",",C2,",",C3)</f>
+        <f>IF(AND(C1="",C2="",C3=""),"",CONCATENATE(IF(C1="","",C1),",",IF(C2="","",C2),",",IF(C3="","",C3)))</f>
       </c>
       <c r="D25" s="43" t="str">
-        <f>CONCATENATE(D1,",",D2,",",D3)</f>
+        <f>IF(AND(D1="",D2="",D3=""),"",CONCATENATE(IF(D1="","",D1),",",IF(D2="","",D2),",",IF(D3="","",D3)))</f>
       </c>
       <c r="E25" s="44"/>
       <c r="G25" s="45" t="str">
-        <f>CONCATENATE(G9," ",G1,"-",G12," .",G10,"-",G11)</f>
+        <f>IF(AND(G9="",G1="",G12="",G10="",G11=""),"",CONCATENATE(IF(G9="","",G9)," ",IF(G1="","",G1),"-",IF(G12="","",G12)," .",IF(G10="","",G10),"-",IF(G11="","",G11)))</f>
       </c>
       <c r="H25" s="45" t="str">
-        <f>CONCATENATE(H9," ",G1,"-",H12,".",H10,"-",H11)</f>
+        <f>IF(AND(H9="",G1="",H12="",H10="",H11=""),"",CONCATENATE(IF(H9="","",H9)," ",IF(G1="","",G1),"-",IF(H12="","",H12),".",IF(H10="","",H10),"-",IF(H11="","",H11)))</f>
       </c>
       <c r="I25" s="45" t="str">
-        <f>CONCATENATE(I9," ",G1,"-",I12," .",I10,"-",I11)</f>
+        <f>IF(AND(I9="",G1="",I12="",I10="",I11=""),"",CONCATENATE(IF(I9="","",I9)," ",IF(G1="","",G1),"-",IF(I12="","",I12)," .",IF(I10="","",I10),"-",IF(I11="","",I11)))</f>
       </c>
     </row>
     <row r="26" spans="1:9" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="46" t="str">
-        <f>CONCATENATE(C8," ",C1,"-",C11,".",C9)</f>
+        <f>IF(AND(C8="",C1="",C11="",C9=""),"",CONCATENATE(IF(C8="","",C8)," ",IF(C1="","",C1),"-",IF(C11="","",C11),".",IF(C9="","",C9)))</f>
       </c>
       <c r="D26" s="46" t="str">
-        <f>CONCATENATE(D8," ",D1,"-",D11,".",D9)</f>
+        <f>IF(AND(D8="",D1="",D11="",D9=""),"",CONCATENATE(IF(D8="","",D8)," ",IF(D1="","",D1),"-",IF(D11="","",D11),".",IF(D9="","",D9)))</f>
       </c>
       <c r="E26" s="47"/>
       <c r="G26" s="45" t="str">
-        <f>CONCATENATE(G9," ",G1,"-",G12)</f>
+        <f>IF(AND(G9="",G1="",G12=""),"",CONCATENATE(IF(G9="","",G9)," ",IF(G1="","",G1),"-",IF(G12="","",G12)))</f>
       </c>
       <c r="H26" s="45" t="str">
-        <f>CONCATENATE(H9," ",G1," ",H12)</f>
+        <f>IF(AND(H9="",G1="",H12=""),"",CONCATENATE(IF(H9="","",H9)," ",IF(G1="","",G1)," ",IF(H12="","",H12)))</f>
       </c>
       <c r="I26" s="45" t="str">
-        <f>CONCATENATE(I9," ",G1,"-",I12)</f>
+        <f>IF(AND(I9="",G1="",I12=""),"",CONCATENATE(IF(I9="","",I9)," ",IF(G1="","",G1),"-",IF(I12="","",I12)))</f>
       </c>
     </row>
     <row r="27" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="46" t="str">
-        <f>CONCATENATE(C8," ",C1)</f>
+        <f>IF(AND(C8="",C1=""),"",CONCATENATE(IF(C8="","",C8)," ",IF(C1="","",C1)))</f>
       </c>
       <c r="D27" s="46" t="str">
-        <f>CONCATENATE(D8," ",D1)</f>
+        <f>IF(AND(D8="",D1=""),"",CONCATENATE(IF(D8="","",D8)," ",IF(D1="","",D1)))</f>
       </c>
       <c r="E27" s="47"/>
       <c r="G27" s="45" t="str">
-        <f>CONCATENATE(G9," ",G1)</f>
+        <f>IF(AND(G9="",G1=""),"",CONCATENATE(IF(G9="","",G9)," ",IF(G1="","",G1)))</f>
       </c>
       <c r="H27" s="45" t="str">
-        <f>CONCATENATE(H9," ",G1)</f>
+        <f>IF(AND(H9="",G1=""),"",CONCATENATE(IF(H9="","",H9)," ",IF(G1="","",G1)))</f>
       </c>
       <c r="I27" s="45" t="str">
-        <f>CONCATENATE(I9," ",G1)</f>
+        <f>IF(AND(I9="",G1=""),"",CONCATENATE(IF(I9="","",I9)," ",IF(G1="","",G1)))</f>
       </c>
     </row>
     <row r="28" spans="1:9" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="48" t="str">
-        <f>CONCATENATE(C19," ",C1,"-",C21,".",C20)</f>
+        <f>IF(AND(C19="",C1="",C21="",C20=""),"",CONCATENATE(IF(C19="","",C19)," ",IF(C1="","",C1),"-",IF(C21="","",C21),".",IF(C20="","",C20)))</f>
       </c>
       <c r="D28" s="48" t="str">
-        <f>CONCATENATE(D19," ",D1,"-",D21,".",D20)</f>
+        <f>IF(AND(D19="",D1="",D21="",D20=""),"",CONCATENATE(IF(D19="","",D19)," ",IF(D1="","",D1),"-",IF(D21="","",D21),".",IF(D20="","",D20)))</f>
       </c>
       <c r="E28" s="45"/>
       <c r="G28" s="2" t="str">
-        <f>CONCATENATE(G6," ",G1," ",G7)</f>
+        <f>IF(AND(G6="",G1="",G7=""),"",CONCATENATE(IF(G6="","",G6)," ",IF(G1="","",G1)," ",IF(G7="","",G7)))</f>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="str">
-        <f>CONCATENATE(I6," ",G1," ",I7)</f>
+        <f>IF(AND(I6="",G1="",I7=""),"",CONCATENATE(IF(I6="","",I6)," ",IF(G1="","",G1)," ",IF(I7="","",I7)))</f>
       </c>
     </row>
     <row r="29" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="48" t="str">
-        <f>CONCATENATE(C19," ",C1," ",C21)</f>
+        <f>IF(AND(C19="",C1="",C21=""),"",CONCATENATE(IF(C19="","",C19)," ",IF(C1="","",C1)," ",IF(C21="","",C21)))</f>
       </c>
       <c r="D29" s="48" t="str">
-        <f>CONCATENATE(D19," ",D1,"-",D21)</f>
+        <f>IF(AND(D19="",D1="",D21=""),"",CONCATENATE(IF(D19="","",D19)," ",IF(D1="","",D1),"-",IF(D21="","",D21)))</f>
       </c>
       <c r="E29" s="45"/>
       <c r="G29" s="49" t="str">
-        <f>CONCATENATE(G16," ",G1," ",G17)</f>
+        <f>IF(AND(G16="",G1="",G17=""),"",CONCATENATE(IF(G16="","",G16)," ",IF(G1="","",G1)," ",IF(G17="","",G17)))</f>
       </c>
       <c r="H29" s="49"/>
       <c r="I29" s="49" t="str">
-        <f>CONCATENATE(I16," ",G1," ",I17)</f>
+        <f>IF(AND(I16="",G1="",I17=""),"",CONCATENATE(IF(I16="","",I16)," ",IF(G1="","",G1)," ",IF(I17="","",I17)))</f>
       </c>
     </row>
     <row r="30" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="50" t="str">
-        <f>CONCATENATE(C19," ",C1)</f>
+        <f>IF(AND(C19="",C1=""),"",CONCATENATE(IF(C19="","",C19)," ",IF(C1="","",C1)))</f>
       </c>
       <c r="D30" s="48" t="str">
-        <f>CONCATENATE(D19," ",D1)</f>
+        <f>IF(AND(D19="",D1=""),"",CONCATENATE(IF(D19="","",D19)," ",IF(D1="","",D1)))</f>
       </c>
       <c r="E30" s="45"/>
       <c r="G30" s="2" t="str">
-        <f>CONCATENATE(G18," ",G1," ",G19)</f>
+        <f>IF(AND(G18="",G1="",G19=""),"",CONCATENATE(IF(G18="","",G18)," ",IF(G1="","",G1)," ",IF(G19="","",G19)))</f>
       </c>
       <c r="H30" s="2"/>
     </row>
@@ -3629,25 +3629,25 @@
       <c r="A11" s="59"/>
       <c r="B11" s="60"/>
     </row>
-    <row r="12" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
         <v>158</v>
       </c>
       <c r="B12" s="60"/>
     </row>
-    <row r="13" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="s">
         <v>159</v>
       </c>
       <c r="B13" s="61"/>
     </row>
-    <row r="14" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="59" t="s">
         <v>160</v>
       </c>
       <c r="B14" s="60"/>
     </row>
-    <row r="15" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="s">
         <v>161</v>
       </c>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="B17" s="62"/>
       <c r="C17" s="63" t="str">
-        <f>CONCATENATE(B17," ",B18," ",B19)</f>
+        <f>IF(AND(B17="",B18="",B19=""),"",CONCATENATE(IF(B17="","",B17)," ",IF(B18="","",B18)," ",IF(B19="","",B19)))</f>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -3694,8 +3694,8 @@
         <v>166</v>
       </c>
       <c r="B21" s="62"/>
-      <c r="C21" s="63" t="str">
-        <f>CONCATENATE(B20," ",B17," ",B21)</f>
+      <c r="C21" s="63">
+        <f>IF(B20="","",IF(AND(B20="",B17="",B21=""),"",CONCATENATE(IF(B20="","",B20)," ",IF(B17="","",B17)," ",IF(B21="","",B21))))</f>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -3703,8 +3703,8 @@
         <v>165</v>
       </c>
       <c r="B22" s="62"/>
-      <c r="C22" s="63" t="str">
-        <f>CONCATENATE(B22," ",B17)</f>
+      <c r="C22" s="63">
+        <f>IF(B22="","",IF(AND(B22="",B17=""),"",CONCATENATE(IF(B22="","",B22)," ",IF(B17="","",B17))))</f>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -3712,8 +3712,8 @@
         <v>167</v>
       </c>
       <c r="B23" s="141"/>
-      <c r="C23" s="64" t="str">
-        <f>CONCATENATE(B22," ",B17," ",B23)</f>
+      <c r="C23" s="64">
+        <f>IF(B22="","",IF(AND(B22="",B17="",B23=""),"",CONCATENATE(IF(B22="","",B22)," ",IF(B17="","",B17)," ",IF(B23="","",B23))))</f>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -3721,8 +3721,8 @@
         <v>168</v>
       </c>
       <c r="B24" s="62"/>
-      <c r="C24" s="64" t="str">
-        <f>CONCATENATE(B22," ",B17," ",B23,".",B24)</f>
+      <c r="C24" s="64">
+        <f>IF(B22="","",IF(AND(B22="",B17="",B23="",B24=""),"",CONCATENATE(IF(B22="","",B22)," ",IF(B17="","",B17)," ",IF(B23="","",B23),".",IF(B24="","",B24))))</f>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -3735,8 +3735,8 @@
         <v>165</v>
       </c>
       <c r="B26" s="62"/>
-      <c r="C26" s="63" t="str">
-        <f>CONCATENATE(B26," ",B17)</f>
+      <c r="C26" s="63">
+        <f>IF(B26="","",IF(AND(B26="",B17=""),"",CONCATENATE(IF(B26="","",B26)," ",IF(B17="","",B17))))</f>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -3744,8 +3744,8 @@
         <v>167</v>
       </c>
       <c r="B27" s="62"/>
-      <c r="C27" s="64" t="str">
-        <f>CONCATENATE(B26," ",B17," ",B27)</f>
+      <c r="C27" s="64">
+        <f>IF(B26="","",IF(AND(B26="",B17="",B27=""),"",CONCATENATE(IF(B26="","",B26)," ",IF(B17="","",B17)," ",IF(B27="","",B27))))</f>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -3753,8 +3753,8 @@
         <v>168</v>
       </c>
       <c r="B28" s="62"/>
-      <c r="C28" s="64" t="str">
-        <f>CONCATENATE(B26," ",B17," ",B27,".",B28)</f>
+      <c r="C28" s="64">
+        <f>IF(B26="","",IF(AND(B26="",B17="",B27="",B28=""),"",CONCATENATE(IF(B26="","",B26)," ",IF(B17="","",B17)," ",IF(B27="","",B27),".",IF(B28="","",B28))))</f>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
@@ -3774,7 +3774,7 @@
         <v>164</v>
       </c>
       <c r="B31" s="66" t="str">
-        <f>'Данные организации'!F2</f>
+        <f>IF('Данные организации'!F2="","",'Данные организации'!F2)</f>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -3782,7 +3782,7 @@
         <v>136</v>
       </c>
       <c r="B32" s="66" t="str">
-        <f>'Данные организации'!F3</f>
+        <f>IF('Данные организации'!F3="","",'Данные организации'!F3)</f>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3790,8 +3790,8 @@
         <v>165</v>
       </c>
       <c r="B33" s="67"/>
-      <c r="C33" s="51" t="str">
-        <f>CONCATENATE(B33," ",B30)</f>
+      <c r="C33" s="51">
+        <f>IF(B33="","",IF(AND(B33="",B30=""),"",CONCATENATE(IF(B33="","",B33)," ",IF(B30="","",B30))))</f>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3799,8 +3799,8 @@
         <v>167</v>
       </c>
       <c r="B34" s="66"/>
-      <c r="C34" s="51" t="str">
-        <f>CONCATENATE(B33," ",B30," ",B34)</f>
+      <c r="C34" s="51">
+        <f>IF(B33="","",IF(AND(B33="",B30="",B34=""),"",CONCATENATE(IF(B33="","",B33)," ",IF(B30="","",B30)," ",IF(B34="","",B34))))</f>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -3808,8 +3808,8 @@
         <v>165</v>
       </c>
       <c r="B35" s="66"/>
-      <c r="C35" s="51" t="str">
-        <f>CONCATENATE(B35," ",B30)</f>
+      <c r="C35" s="51">
+        <f>IF(B35="","",IF(AND(B35="",B30=""),"",CONCATENATE(IF(B35="","",B35)," ",IF(B30="","",B30))))</f>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -3817,8 +3817,8 @@
         <v>167</v>
       </c>
       <c r="B36" s="66"/>
-      <c r="C36" s="51" t="str">
-        <f>CONCATENATE(B35," ",B30," ",B36)</f>
+      <c r="C36" s="51">
+        <f>IF(B35="","",IF(AND(B35="",B30="",B36=""),"",CONCATENATE(IF(B35="","",B35)," ",IF(B30="","",B30)," ",IF(B36="","",B36))))</f>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -3826,8 +3826,8 @@
         <v>165</v>
       </c>
       <c r="B37" s="66"/>
-      <c r="C37" s="51" t="str">
-        <f>CONCATENATE(B37," ",B30)</f>
+      <c r="C37" s="51">
+        <f>IF(B37="","",IF(AND(B37="",B30=""),"",CONCATENATE(IF(B37="","",B37)," ",IF(B30="","",B30))))</f>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -3835,15 +3835,15 @@
         <v>167</v>
       </c>
       <c r="B38" s="66"/>
-      <c r="C38" s="51" t="str">
-        <f>CONCATENATE(B37," ",B30," ",B38)</f>
+      <c r="C38" s="51">
+        <f>IF(B37="","",IF(AND(B37="",B30="",B38=""),"",CONCATENATE(IF(B37="","",B37)," ",IF(B30="","",B30)," ",IF(B38="","",B38))))</f>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="65"/>
       <c r="B39" s="66"/>
-      <c r="C39" s="51" t="str">
-        <f>CONCATENATE(B33," ",B30," ",B34," ",B39)</f>
+      <c r="C39" s="51">
+        <f>IF(B33="","",IF(AND(B33="",B30="",B34="",B39=""),"",CONCATENATE(IF(B33="","",B33)," ",IF(B30="","",B30)," ",IF(B34="","",B34)," ",IF(B39="","",B39))))</f>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3851,8 +3851,8 @@
         <v>165</v>
       </c>
       <c r="B40" s="66"/>
-      <c r="C40" s="51" t="str">
-        <f>CONCATENATE(B40," ",B30)</f>
+      <c r="C40" s="51">
+        <f>IF(B40="","",IF(AND(B40="",B30=""),"",CONCATENATE(IF(B40="","",B40)," ",IF(B30="","",B30))))</f>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3860,8 +3860,8 @@
         <v>167</v>
       </c>
       <c r="B41" s="66"/>
-      <c r="C41" s="68" t="str">
-        <f>CONCATENATE(B40," ",B30," ",B41)</f>
+      <c r="C41" s="68">
+        <f>IF(B40="","",IF(AND(B40="",B30="",B41=""),"",CONCATENATE(IF(B40="","",B40)," ",IF(B30="","",B30)," ",IF(B41="","",B41))))</f>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3869,8 +3869,8 @@
         <v>168</v>
       </c>
       <c r="B42" s="66"/>
-      <c r="C42" s="51" t="str">
-        <f>CONCATENATE(B40," ",B30," ",B41,".",B42)</f>
+      <c r="C42" s="51">
+        <f>IF(B40="","",IF(AND(B40="",B30="",B41="",B42=""),"",CONCATENATE(IF(B40="","",B40)," ",IF(B30="","",B30)," ",IF(B41="","",B41),".",IF(B42="","",B42))))</f>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3885,8 +3885,8 @@
         <v>165</v>
       </c>
       <c r="B44" s="69"/>
-      <c r="C44" s="51" t="str">
-        <f>CONCATENATE(B44," ",B30)</f>
+      <c r="C44" s="51">
+        <f>IF(B44="","",IF(AND(B44="",B30=""),"",CONCATENATE(IF(B44="","",B44)," ",IF(B30="","",B30))))</f>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3894,8 +3894,8 @@
         <v>167</v>
       </c>
       <c r="B45" s="69"/>
-      <c r="C45" s="51" t="str">
-        <f>CONCATENATE(B44," ",B30," ",B45)</f>
+      <c r="C45" s="51">
+        <f>IF(B44="","",IF(AND(B44="",B30="",B45=""),"",CONCATENATE(IF(B44="","",B44)," ",IF(B30="","",B30)," ",IF(B45="","",B45))))</f>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3903,8 +3903,8 @@
         <v>168</v>
       </c>
       <c r="B46" s="69"/>
-      <c r="C46" s="51" t="str">
-        <f>CONCATENATE(B44," ",B30," ",B45,".",B46)</f>
+      <c r="C46" s="51">
+        <f>IF(B44="","",IF(AND(B44="",B30="",B45="",B46=""),"",CONCATENATE(IF(B44="","",B44)," ",IF(B30="","",B30)," ",IF(B45="","",B45),".",IF(B46="","",B46))))</f>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3912,8 +3912,8 @@
         <v>165</v>
       </c>
       <c r="B47" s="69"/>
-      <c r="C47" s="51" t="str">
-        <f>CONCATENATE(B47," ",B30)</f>
+      <c r="C47" s="51">
+        <f>IF(B47="","",IF(AND(B47="",B30=""),"",CONCATENATE(IF(B47="","",B47)," ",IF(B30="","",B30))))</f>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -3921,8 +3921,8 @@
         <v>167</v>
       </c>
       <c r="B48" s="66"/>
-      <c r="C48" s="51" t="str">
-        <f>CONCATENATE(B47," ",B30," ",B48)</f>
+      <c r="C48" s="51">
+        <f>IF(B47="","",IF(AND(B47="",B30="",B48=""),"",CONCATENATE(IF(B47="","",B47)," ",IF(B30="","",B30)," ",IF(B48="","",B48))))</f>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
@@ -3966,7 +3966,7 @@
         <v>172</v>
       </c>
       <c r="B55" s="70" t="str">
-        <f>B3</f>
+        <f>IF(B3="","",B3)</f>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -3984,8 +3984,8 @@
         <v>163</v>
       </c>
       <c r="B58" s="71"/>
-      <c r="C58" s="51" t="str">
-        <f>CONCATENATE(B62," ",B58," ",B63)</f>
+      <c r="C58" s="51">
+        <f>IF(B62="","",IF(AND(B62="",B58="",B63=""),"",CONCATENATE(IF(B62="","",B62)," ",IF(B58="","",B58)," ",IF(B63="","",B63))))</f>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -5148,7 +5148,7 @@
         <v>47</v>
       </c>
       <c r="F23" s="180" t="str">
-        <f>'Данные объект'!B2</f>
+        <f>IF('Данные объект'!B2="","",'Данные объект'!B2)</f>
       </c>
       <c r="G23" s="180"/>
       <c r="H23" s="138"/>
@@ -5668,9 +5668,7 @@
       <c r="P4" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="201" t="str">
-        <f>'Данные объект'!B2</f>
-      </c>
+      <c r="Q4" s="201"/>
       <c r="R4" s="201"/>
       <c r="S4" s="201"/>
       <c r="T4" s="201"/>
@@ -5773,7 +5771,7 @@
     </row>
     <row r="8" spans="1:36" s="17" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A8" s="181" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B8" s="181"/>
       <c r="C8" s="181"/>
@@ -5917,9 +5915,7 @@
       <c r="J12" s="87"/>
     </row>
     <row r="13" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A13" s="184" t="str">
-        <f>'Данные объект'!B17</f>
-      </c>
+      <c r="A13" s="184"/>
       <c r="B13" s="184"/>
       <c r="C13" s="184"/>
       <c r="D13" s="184"/>
@@ -5997,9 +5993,7 @@
       <c r="AJ14" s="202"/>
     </row>
     <row r="15" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="184" t="str">
-        <f>'Данные объект'!B18</f>
-      </c>
+      <c r="A15" s="184"/>
       <c r="B15" s="184"/>
       <c r="C15" s="184"/>
       <c r="D15" s="184"/>
@@ -6077,9 +6071,7 @@
       <c r="AJ16" s="202"/>
     </row>
     <row r="17" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="184" t="str">
-        <f>'Данные объект'!B19</f>
-      </c>
+      <c r="A17" s="184"/>
       <c r="B17" s="184"/>
       <c r="C17" s="184"/>
       <c r="D17" s="184"/>
@@ -6569,8 +6561,8 @@
       <c r="J30" s="93"/>
     </row>
     <row r="31" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A31" s="184" t="str">
-        <f>CONCATENATE('Данные объект'!B30," ",'Данные объект'!B31)</f>
+      <c r="A31" s="184">
+        <f>IF(AND('Данные объект'!B30="",'Данные объект'!B31="",'Данные объект'!B32=""),"",CONCATENATE(IF('Данные объект'!B30="","",'Данные объект'!B30)," ",IF('Данные объект'!B31="","",'Данные объект'!B31)," ",IF('Данные объект'!B32="","",'Данные объект'!B32)))</f>
       </c>
       <c r="B31" s="184"/>
       <c r="C31" s="184"/>
@@ -6649,9 +6641,7 @@
       <c r="AJ32" s="202"/>
     </row>
     <row r="33" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A33" s="184" t="str">
-        <f>'Данные объект'!B32</f>
-      </c>
+      <c r="A33" s="184"/>
       <c r="B33" s="184"/>
       <c r="C33" s="184"/>
       <c r="D33" s="184"/>
@@ -6884,7 +6874,7 @@
       <c r="A39" s="188"/>
       <c r="B39" s="188"/>
       <c r="C39" s="188" t="str">
-        <f>'Данные объект'!B34</f>
+        <f>IF('Данные объект'!B34="","",'Данные объект'!B34)</f>
       </c>
       <c r="D39" s="188"/>
       <c r="E39" s="188"/>
@@ -6893,14 +6883,14 @@
       <c r="H39" s="188"/>
       <c r="I39" s="188"/>
       <c r="J39" s="188" t="str">
-        <f>'Данные объект'!C33</f>
+        <f>IF('Данные объект'!C33="","",'Данные объект'!C33)</f>
       </c>
       <c r="K39" s="188"/>
       <c r="L39" s="188"/>
       <c r="M39" s="188"/>
       <c r="N39" s="188"/>
       <c r="O39" s="233" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="P39" s="233"/>
       <c r="Q39" s="233"/>
@@ -7811,7 +7801,7 @@
     </row>
     <row r="65" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A65" s="184" t="str">
-        <f>'Данные объект'!B50</f>
+        <f>IF('Данные объект'!B50="","",'Данные объект'!B50)</f>
       </c>
       <c r="B65" s="184"/>
       <c r="C65" s="184"/>
@@ -7890,8 +7880,8 @@
       <c r="AJ66" s="202"/>
     </row>
     <row r="67" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A67" s="184" t="str">
-        <f>'Данные объект'!B51</f>
+      <c r="A67" s="184">
+        <f>IF(AND('Данные объект'!B51="",'Данные объект'!B52=""),"",CONCATENATE(IF('Данные объект'!B51="","",'Данные объект'!B51)," ",IF('Данные объект'!B52="","",'Данные объект'!B52)))</f>
       </c>
       <c r="B67" s="184"/>
       <c r="C67" s="184"/>
@@ -7970,9 +7960,7 @@
       <c r="AJ68" s="202"/>
     </row>
     <row r="69" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A69" s="184" t="str">
-        <f>'Данные объект'!B52</f>
-      </c>
+      <c r="A69" s="184"/>
       <c r="B69" s="184"/>
       <c r="C69" s="184"/>
       <c r="D69" s="184"/>
@@ -8537,7 +8525,9 @@
       <c r="J84" s="103"/>
     </row>
     <row r="85" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A85" s="184"/>
+      <c r="A85" s="184">
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
+      </c>
       <c r="B85" s="184"/>
       <c r="C85" s="184"/>
       <c r="D85" s="184"/>
@@ -8615,7 +8605,9 @@
       <c r="AJ86" s="202"/>
     </row>
     <row r="87" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A87" s="184"/>
+      <c r="A87" s="184">
+        <f>IF(AND('Данные объект'!B18="",'Данные объект'!B19=""),"",CONCATENATE(IF('Данные объект'!B18="","",'Данные объект'!B18)," ",IF('Данные объект'!B19="","",'Данные объект'!B19)))</f>
+      </c>
       <c r="B87" s="184"/>
       <c r="C87" s="184"/>
       <c r="D87" s="184"/>
@@ -8952,7 +8944,7 @@
       <c r="A95" s="188"/>
       <c r="B95" s="188"/>
       <c r="C95" s="188" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="D95" s="188"/>
       <c r="E95" s="188"/>
@@ -8961,21 +8953,21 @@
       <c r="H95" s="188"/>
       <c r="I95" s="188"/>
       <c r="J95" s="188" t="str">
-        <f>'Данные объект'!C22</f>
+        <f>IF('Данные объект'!C22="","",'Данные объект'!C22)</f>
       </c>
       <c r="K95" s="188"/>
       <c r="L95" s="188"/>
       <c r="M95" s="188"/>
       <c r="N95" s="188"/>
       <c r="O95" s="188" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="P95" s="188"/>
       <c r="Q95" s="188"/>
       <c r="R95" s="188"/>
       <c r="S95" s="188"/>
       <c r="T95" s="188" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="U95" s="188"/>
       <c r="V95" s="188"/>
@@ -8998,7 +8990,7 @@
       <c r="A96" s="188"/>
       <c r="B96" s="188"/>
       <c r="C96" s="188" t="str">
-        <f>'Данные объект'!B27</f>
+        <f>IF('Данные объект'!B27="","",'Данные объект'!B27)</f>
       </c>
       <c r="D96" s="188"/>
       <c r="E96" s="188"/>
@@ -9007,14 +8999,14 @@
       <c r="H96" s="188"/>
       <c r="I96" s="188"/>
       <c r="J96" s="188" t="str">
-        <f>'Данные объект'!C26</f>
+        <f>IF('Данные объект'!C26="","",'Данные объект'!C26)</f>
       </c>
       <c r="K96" s="188"/>
       <c r="L96" s="188"/>
       <c r="M96" s="188"/>
       <c r="N96" s="188"/>
       <c r="O96" s="188" t="str">
-        <f>'Данные объект'!B28</f>
+        <f>IF('Данные объект'!B28="","",'Данные объект'!B28)</f>
       </c>
       <c r="P96" s="188"/>
       <c r="Q96" s="188"/>
@@ -9268,7 +9260,7 @@
       <c r="A103" s="185"/>
       <c r="B103" s="185"/>
       <c r="C103" s="189" t="str">
-        <f>'Данные объект'!B41</f>
+        <f>IF('Данные объект'!B41="","",'Данные объект'!B41)</f>
       </c>
       <c r="D103" s="189"/>
       <c r="E103" s="189"/>
@@ -9282,7 +9274,7 @@
       <c r="M103" s="189"/>
       <c r="N103" s="189"/>
       <c r="O103" s="209" t="str">
-        <f>'Данные объект'!C40</f>
+        <f>IF('Данные объект'!C40="","",'Данные объект'!C40)</f>
       </c>
       <c r="P103" s="209"/>
       <c r="Q103" s="209"/>
@@ -9291,7 +9283,7 @@
       <c r="T103" s="209"/>
       <c r="U103" s="209"/>
       <c r="V103" s="188" t="str">
-        <f>CONCATENATE('Данные объект'!B42," ",'Данные объект'!B43)</f>
+        <f>IF(AND('Данные объект'!B42="",'Данные объект'!B43=""),"",CONCATENATE(IF('Данные объект'!B42="","",'Данные объект'!B42)," ",IF('Данные объект'!B43="","",'Данные объект'!B43)))</f>
       </c>
       <c r="W103" s="188"/>
       <c r="X103" s="188"/>
@@ -9852,7 +9844,7 @@
       <c r="A119" s="185"/>
       <c r="B119" s="185"/>
       <c r="C119" s="185" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="D119" s="185"/>
       <c r="E119" s="185"/>
@@ -9866,7 +9858,7 @@
       <c r="M119" s="185"/>
       <c r="N119" s="185"/>
       <c r="O119" s="209" t="str">
-        <f>'Данные объект'!C22</f>
+        <f>IF('Данные объект'!C22="","",'Данные объект'!C22)</f>
       </c>
       <c r="P119" s="209"/>
       <c r="Q119" s="209"/>
@@ -9875,7 +9867,7 @@
       <c r="T119" s="209"/>
       <c r="U119" s="209"/>
       <c r="V119" s="188" t="str">
-        <f>CONCATENATE('Данные объект'!B24," ",'Данные объект'!B25)</f>
+        <f>IF(AND('Данные объект'!B24="",'Данные объект'!B25=""),"",CONCATENATE(IF('Данные объект'!B24="","",'Данные объект'!B24)," ",IF('Данные объект'!B25="","",'Данные объект'!B25)))</f>
       </c>
       <c r="W119" s="188"/>
       <c r="X119" s="188"/>
@@ -11920,7 +11912,7 @@
     </row>
     <row r="176" spans="1:36" s="88" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="203" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B176" s="203"/>
       <c r="C176" s="203"/>
@@ -12000,7 +11992,7 @@
     </row>
     <row r="178" spans="1:36" s="88" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A178" s="184" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B178" s="184"/>
       <c r="C178" s="184"/>
@@ -12140,7 +12132,7 @@
       <c r="F182" s="113"/>
       <c r="G182" s="113"/>
       <c r="H182" s="216">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="I182" s="216"/>
       <c r="J182" s="216"/>
@@ -12262,7 +12254,7 @@
       <c r="F185" s="113"/>
       <c r="G185" s="113"/>
       <c r="H185" s="216">
-        <f>'Данные объект'!B8</f>
+        <f>IF('Данные объект'!B8="","",'Данные объект'!B8)</f>
       </c>
       <c r="I185" s="216"/>
       <c r="J185" s="216"/>
@@ -12525,7 +12517,7 @@
       <c r="S195" s="187"/>
       <c r="T195" s="187"/>
       <c r="V195" s="219" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="W195" s="219"/>
       <c r="X195" s="219"/>
@@ -14269,13 +14261,13 @@
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
       <c r="D5" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="E5" s="142">
-        <f>'Данные объект'!B8</f>
+        <f>IF('Данные объект'!B8="","",'Данные объект'!B8)</f>
       </c>
       <c r="F5" s="155" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
     </row>
     <row r="6" spans="1:6" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -14283,13 +14275,13 @@
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
       <c r="D6" s="130">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="E6" s="130">
-        <f>'Данные объект'!B8</f>
+        <f>IF('Данные объект'!B8="","",'Данные объект'!B8)</f>
       </c>
       <c r="F6" s="155" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
     </row>
     <row r="7" spans="1:6" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -14297,13 +14289,13 @@
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
       <c r="D7" s="130">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="E7" s="130">
-        <f>'Данные объект'!B8</f>
+        <f>IF('Данные объект'!B8="","",'Данные объект'!B8)</f>
       </c>
       <c r="F7" s="155" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
     </row>
     <row r="8" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -14717,7 +14709,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="23"/>
       <c r="C5" s="143" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="D5" s="131"/>
       <c r="E5" s="23"/>
@@ -15644,11 +15636,11 @@
       <c r="C5" s="159"/>
       <c r="D5" s="158"/>
       <c r="E5" s="157" t="str">
-        <f>'Данные объект'!C41</f>
+        <f>IF('Данные объект'!C41="","",'Данные объект'!C41)</f>
       </c>
       <c r="F5" s="156"/>
       <c r="G5" s="157" t="str">
-        <f>'Данные объект'!C41</f>
+        <f>IF('Данные объект'!C41="","",'Данные объект'!C41)</f>
       </c>
     </row>
     <row r="6" spans="1:7" s="17" customFormat="1" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -15657,11 +15649,11 @@
       <c r="C6" s="159"/>
       <c r="D6" s="158"/>
       <c r="E6" s="144" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="F6" s="156"/>
       <c r="G6" s="144" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
     </row>
     <row r="7" spans="1:7" s="17" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.25">
